--- a/data/out/cities.xlsx
+++ b/data/out/cities.xlsx
@@ -422,9 +422,9 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,97 +435,97 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>founded</t>
+          <t>population</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>SPB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Центральный федеральный округ</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>5384342</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Санкт-Петербург</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Северо-Западный федеральный округ</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1703</t>
+          <t>13010112</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Казань</t>
+          <t>Kazan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Приволжский федеральный округ</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1306953</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Новосибирск</t>
+          <t>Novosibirsk</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Сибирский федеральный округ</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1620162</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Екатеринбург</t>
+          <t>Yekaterinburg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Уральский федеральный округ</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1493749</t>
         </is>
       </c>
     </row>
